--- a/faq.xlsx
+++ b/faq.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutomatedTelegram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A1295E-23FD-459C-BB93-707A2FD2342C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623B89A7-86EF-458F-8E01-748E9176CF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,9 +40,6 @@
     <t>Our basic plan starts at $10/month.</t>
   </si>
   <si>
-    <t>Location</t>
-  </si>
-  <si>
     <t>where, address, location</t>
   </si>
   <si>
@@ -83,6 +80,9 @@
   </si>
   <si>
     <t>How much does it cost?, ថ្លៃប៉ុន្មាន?</t>
+  </si>
+  <si>
+    <t>ទីតាំង</t>
   </si>
 </sst>
 </file>
@@ -451,13 +451,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -468,16 +468,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -485,16 +485,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -502,16 +502,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/faq.xlsx
+++ b/faq.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutomatedTelegram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623B89A7-86EF-458F-8E01-748E9176CF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B61308-807D-4CC3-B0BD-7CD17A96327C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="85">
   <si>
     <t>id</t>
   </si>
@@ -40,36 +40,15 @@
     <t>Our basic plan starts at $10/month.</t>
   </si>
   <si>
-    <t>where, address, location</t>
-  </si>
-  <si>
-    <t>Where are you located?</t>
-  </si>
-  <si>
     <t>We are located at 123 Main St.</t>
   </si>
   <si>
-    <t>Hours</t>
-  </si>
-  <si>
-    <t>time, open, close, hours</t>
-  </si>
-  <si>
     <t>What are your business hours?</t>
   </si>
   <si>
     <t>We are open 9 AM to 5 PM, Mon-Fri.</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>How to deposit money?</t>
-  </si>
-  <si>
-    <t>Deposit</t>
-  </si>
-  <si>
     <t>You can click on the deposit tab-&gt;Scan QR to process it.</t>
   </si>
   <si>
@@ -83,6 +62,219 @@
   </si>
   <si>
     <t>ទីតាំង</t>
+  </si>
+  <si>
+    <t>ស្វាគមន៍</t>
+  </si>
+  <si>
+    <t>សួស្តី, Hi, ជំរាបសួ</t>
+  </si>
+  <si>
+    <t>សួស្តីបង តើបងមានបញ្ហាអ្វីដែរ?</t>
+  </si>
+  <si>
+    <t>ម៉ោង</t>
+  </si>
+  <si>
+    <t>time, open, close, hours, ម៉ោង, ពេល</t>
+  </si>
+  <si>
+    <t>where, address, location, កន្លែង, ទីតាំងធ្វើការ</t>
+  </si>
+  <si>
+    <t>Where are you located? តើនៅកន្លែងណា?</t>
+  </si>
+  <si>
+    <t>ដាក់ប្រាក់</t>
+  </si>
+  <si>
+    <t>Deposit, ដាក់ប្រាក់</t>
+  </si>
+  <si>
+    <t>How to deposit money? តើដាក់ប្រាក់របៀបណា?</t>
+  </si>
+  <si>
+    <t>តើគោលការណ៍បង្វិលសងប្រាក់/ប្រគល់ទំនិញវិញរបស់អ្នកមានអ្វីខ្លះ?</t>
+  </si>
+  <si>
+    <t>យើងផ្តល់ជូននូវគោលការណ៍ប្រគល់ទំនិញវិញក្នុងរយៈពេល 30 ថ្ងៃ សម្រាប់រាល់ទំនិញដែលមិនទាន់ប្រើប្រាស់ និងនៅក្នុងការវេចខ្ចប់ដើម។</t>
+  </si>
+  <si>
+    <t>តើការដឹកជញ្ជូនប្រើរយៈពេលប៉ុន្មាន?</t>
+  </si>
+  <si>
+    <t>ការដឹកជញ្ជូនធម្មតាជាទូទៅចំណាយពេល 3-5 ថ្ងៃធ្វើការ ខណៈការដឹកជញ្ជូនរហ័សចំណាយពេល 1-2 ថ្ងៃធ្វើការ។</t>
+  </si>
+  <si>
+    <t>តើអ្នកមានសេវាកម្មដឹកជញ្ជូនអន្តរជាតិដែរឬទេ?</t>
+  </si>
+  <si>
+    <t>បាទ/ចាស យើងដឹកជញ្ជូនទៅកាន់ជាង 50 ប្រទេសទូទាំងពិភពលោក។ ពេលវេលាដឹកជញ្ជូនអាចប្រែប្រួលអាស្រ័យលើទីតាំង។</t>
+  </si>
+  <si>
+    <t>តើខ្ញុំអាចតាមដានការបញ្ជាទិញរបស់ខ្ញុំដោយរបៀបណា?</t>
+  </si>
+  <si>
+    <t>ពេលទំនិញរបស់អ្នកត្រូវបានបញ្ជូនចេញ អ្នកនឹងទទួលបានអ៊ីមែលដែលមានលេខកូដតាមដាន និងតំណភ្ជាប់ដើម្បីតាមដានកញ្ចប់ឥវ៉ាន់របស់អ្នក។</t>
+  </si>
+  <si>
+    <t>តើអ្នកទទួលយកវិធីសាស្ត្រទូទាត់ប្រាក់អ្វីខ្លះ?</t>
+  </si>
+  <si>
+    <t>យើងទទួលយកកាតឥណទានធំៗទាំងអស់ (Visa, MasterCard, American Express, Discover), PayPal, និង Apple Pay។</t>
+  </si>
+  <si>
+    <t>តើខ្ញុំអាចផ្លាស់ប្តូរ ឬលុបចោលការបញ្ជាទិញរបស់ខ្ញុំបានទេ?</t>
+  </si>
+  <si>
+    <t>ការបញ្ជាទិញអាចផ្លាស់ប្តូរ ឬលុបចោលបានក្នុងរយៈពេល 24 ម៉ោងបន្ទាប់ពីបានបញ្ជាទិញ។ សូមទាក់ទងក្រុមការងារផ្នែកគាំទ្ររបស់យើងជាបន្ទាន់។</t>
+  </si>
+  <si>
+    <t>តើខ្ញុំអាចទាក់ទងផ្នែកសេវាកម្មអតិថិជនដោយរបៀបណា?</t>
+  </si>
+  <si>
+    <t>អ្នកអាចទាក់ទងក្រុមការងារផ្នែកគាំទ្ររបស់យើងតាមរយៈអ៊ីមែល support@example.com, តាមរយៈសារផ្ទាល់ (live chat), ឬទូរស័ព្ទទៅលេខ 1-800-123-4567។</t>
+  </si>
+  <si>
+    <t>តើព័ត៌មានផ្ទាល់ខ្លួន និងព័ត៌មានទូទាត់ប្រាក់របស់ខ្ញុំមានសុវត្ថិភាពដែរឬទេ?</t>
+  </si>
+  <si>
+    <t>បាទ/ចាស គេហទំព័ររបស់យើងប្រើប្រាស់ប្រព័ន្ធកូដនីយកម្ម SSL ស្តង់ដារដើម្បីការពារព័ត៌មានផ្ទាល់ខ្លួន និងការទូទាត់ប្រាក់របស់អ្នកឱ្យមានសុវត្ថិភាពខ្ពស់បំផុត។</t>
+  </si>
+  <si>
+    <t>តើអ្នកមានការធានាលើផលិតផល/សេវាកម្មរបស់អ្នកដែរឬទេ?</t>
+  </si>
+  <si>
+    <t>បាទ/ចាស ផលិតផលទាំងអស់របស់យើងមានការធានារយៈពេលមួយឆ្នាំពីរោងចក្រ ចំពោះការខូចខាតពីកំណើត។</t>
+  </si>
+  <si>
+    <t>តើខ្ញុំអាចបង្កើតគណនីដោយរបៀបណា?</t>
+  </si>
+  <si>
+    <t>សូមចុចលើប៊ូតុង "ចុះឈ្មោះ" (Sign Up ឬ Register) នៅផ្នែកខាងស្តាំខាងលើនៃទំព័រដើមរបស់យើង រួចបំពេញព័ត៌មានរបស់អ្នក។</t>
+  </si>
+  <si>
+    <t>ខ្ញុំភ្លេចពាក្យសម្ងាត់ តើខ្ញុំត្រូវកំណត់វាឡើងវិញដោយរបៀបណា?</t>
+  </si>
+  <si>
+    <t>សូមចុចលើតំណ "ភ្លេចពាក្យសម្ងាត់" (Forgot Password) នៅលើទំព័រចូលគណនី ហើយយើងនឹងផ្ញើអ៊ីមែលណែនាំពីរបៀបកំណត់វាឡើងវិញជូនអ្នក។</t>
+  </si>
+  <si>
+    <t>តើអ្នកមានលក់កាតកាដូឌីជីថលដែរឬទេ?</t>
+  </si>
+  <si>
+    <t>បាទ/ចាស កាតកាដូឌីជីថលមានដាក់លក់នៅលើគេហទំព័ររបស់យើងក្នុងតម្លៃផ្សេងៗគ្នា ហើយកាតទាំងនេះមិនមានថ្ងៃផុតកំណត់ឡើយ។</t>
+  </si>
+  <si>
+    <t>តើផលិតផលរបស់អ្នកមិនប៉ះពាល់ដល់បរិស្ថានមែនទេ?</t>
+  </si>
+  <si>
+    <t>យើងប្តេជ្ញាចិត្តចំពោះនិរន្តរភាព និងមានផ្តល់ជូននូវខ្សែស្រឡាយផលិតផលដែលមិនប៉ះពាល់ដល់បរិស្ថានផងដែរ។</t>
+  </si>
+  <si>
+    <t>តើផលិតផលរបស់អ្នកត្រូវបានផលិត ឬមានប្រភពមកពីណា?</t>
+  </si>
+  <si>
+    <t>ផលិតផលរបស់យើងត្រូវបានរចនាឡើងនៅសហរដ្ឋអាមេរិក និងផលិតដោយទំនួលខុសត្រូវខ្ពស់នៅក្នុងរោងចក្រនានាជុំវិញពិភពលោក។</t>
+  </si>
+  <si>
+    <t>តើខ្ញុំអាចប្រើលេខកូដបញ្ចុះតម្លៃច្រើនក្នុងការបញ្ជាទិញតែមួយបានទេ?</t>
+  </si>
+  <si>
+    <t>ជាទូទៅ អ្នកអាចប្រើលេខកូដបញ្ចុះតម្លៃតែមួយប៉ុណ្ណោះសម្រាប់ការបញ្ជាទិញមួយ លើកលែងតែមានការបញ្ជាក់ផ្សេងក្នុងអំឡុងពេលមានប្រូម៉ូសិនពិសេស។</t>
+  </si>
+  <si>
+    <t>តើខ្ញុំត្រូវធ្វើដូចម្តេចប្រសិនបើខ្ញុំទទួលបានទំនិញខូចខាត ឬមិនត្រឹមត្រូវ?</t>
+  </si>
+  <si>
+    <t>សូមទាក់ទងផ្នែកសេវាកម្មអតិថិជនក្នុងរយៈពេល 48 ម៉ោងបន្ទាប់ពីទទួលបានទំនិញ ព្រមទាំងភ្ជាប់ជាមួយរូបថតបញ្ជាក់ពីបញ្ហា ហើយយើងនឹងរៀបចំដោះស្រាយជូន។</t>
+  </si>
+  <si>
+    <t>តើអ្នកមានទីតាំងហាងផ្ទាល់ដែរឬទេ?</t>
+  </si>
+  <si>
+    <t>បច្ចុប្បន្ន យើងដំណើរការលក់តែនៅលើអនឡាញប៉ុណ្ណោះ ដើម្បីផ្តល់នូវតម្លៃល្អបំផុត និងភាពងាយស្រួលដល់អតិថិជនរបស់យើងជុំវិញពិភពលោក។</t>
+  </si>
+  <si>
+    <t>តើខ្ញុំត្រូវឈប់ទទួលព្រឹត្តិបត្រព័ត៌មាន (Newsletter) តាមអ៊ីមែលដោយរបៀបណា?</t>
+  </si>
+  <si>
+    <t>អ្នកអាចឈប់ជាវបានយ៉ាងងាយស្រួល ដោយគ្រាន់តែចុចលើតំណ "Unsubscribe" (ឈប់ជាវ) នៅផ្នែកខាងក្រោមនៃអ៊ីមែលផ្សព្វផ្សាយណាមួយរបស់យើង។</t>
+  </si>
+  <si>
+    <t>តើអ្នកមានតម្លៃបោះដុំ ឬការបញ្ចុះតម្លៃសម្រាប់ការទិញច្រើនដែរឬទេ?</t>
+  </si>
+  <si>
+    <t>បាទ/ចាស យើងមានតម្លៃបោះដុំសម្រាប់ការទិញច្រើន។ សូមទាក់ទងក្រុមការងារផ្នែកលក់របស់យើងសម្រាប់ព័ត៌មានលម្អិតបន្ថែម។</t>
+  </si>
+  <si>
+    <t>តើខ្ញុំអាចផ្តល់ការវាយតម្លៃលើផលិតផល ឬសេវាកម្មដោយរបៀបណា?</t>
+  </si>
+  <si>
+    <t>អ្នកអាចផ្តល់ការវាយតម្លៃបាន ដោយចូលទៅកាន់ទំព័រផលិតផលនៅលើគេហទំព័ររបស់យើង រួចអូសចុះក្រោមទៅផ្នែក "ការវាយតម្លៃរបស់អតិថិជន" ឬតាមរយៈការឆ្លើយតបអ៊ីមែលរបស់យើងក្រោយពេលអ្នកបានទិញរួច។</t>
+  </si>
+  <si>
+    <t>Return policy, (គោលការណ៍ប្រគល់ទំនិញវិញ)</t>
+  </si>
+  <si>
+    <t>Shipping time, (ពេលវេលាដឹកជញ្ជូន)</t>
+  </si>
+  <si>
+    <t>International shipping, (ការដឹកជញ្ជូនអន្តរជាតិ)</t>
+  </si>
+  <si>
+    <t>Order tracking, (ការតាមដានការបញ្ជាទិញ)</t>
+  </si>
+  <si>
+    <t>Payment methods, (វិធីសាស្ត្រទូទាត់ប្រាក់)</t>
+  </si>
+  <si>
+    <t>Order modification, (ការផ្លាស់ប្តូរការបញ្ជាទិញ)</t>
+  </si>
+  <si>
+    <t>Customer support, (សេវាកម្មអតិថិជន)</t>
+  </si>
+  <si>
+    <t>Security, (សុវត្ថិភាពទិន្នន័យ)</t>
+  </si>
+  <si>
+    <t>Warranty, (ការធានា)</t>
+  </si>
+  <si>
+    <t>Account creation, (ការបង្កើតគណនី)</t>
+  </si>
+  <si>
+    <t>Password reset, (ការកំណត់ពាក្យសម្ងាត់ឡើងវិញ)</t>
+  </si>
+  <si>
+    <t>Gift cards, (កាតកាដូ)</t>
+  </si>
+  <si>
+    <t>Eco-friendly, (មិនប៉ះពាល់ដល់បរិស្ថាន)</t>
+  </si>
+  <si>
+    <t>Manufacturing, (ប្រភពផលិតកម្ម)</t>
+  </si>
+  <si>
+    <t>Discounts, (ការបញ្ចុះតម្លៃ)</t>
+  </si>
+  <si>
+    <t>Damaged items, (ទំនិញខូចខាត)</t>
+  </si>
+  <si>
+    <t>Physical store, (ទីតាំងហាងផ្ទាល់)</t>
+  </si>
+  <si>
+    <t>Unsubscribe, (ឈប់ជាវព័ត៌មាន)</t>
+  </si>
+  <si>
+    <t>Wholesale, (ការទិញបោះដុំ)</t>
+  </si>
+  <si>
+    <t>Reviews, (ការវាយតម្លៃ)</t>
+  </si>
+  <si>
+    <t>ព័ត៌មានទូទៅ</t>
   </si>
 </sst>
 </file>
@@ -422,11 +614,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="21.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -451,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -468,16 +660,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -485,16 +677,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -502,19 +694,380 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="B16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17">
         <v>16</v>
       </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" t="s">
+        <v>61</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C7:F45">
+    <sortCondition ref="C7:C45"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/faq.xlsx
+++ b/faq.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutomatedTelegram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B61308-807D-4CC3-B0BD-7CD17A96327C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1B7CB9-9E65-405F-930C-1C73022FBEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -241,9 +241,6 @@
     <t>Warranty, (ការធានា)</t>
   </si>
   <si>
-    <t>Account creation, (ការបង្កើតគណនី)</t>
-  </si>
-  <si>
     <t>Password reset, (ការកំណត់ពាក្យសម្ងាត់ឡើងវិញ)</t>
   </si>
   <si>
@@ -275,6 +272,9 @@
   </si>
   <si>
     <t>ព័ត៌មានទូទៅ</t>
+  </si>
+  <si>
+    <t>Account creation, (ការបង្កើតគណនី), បើកអាខោន</t>
   </si>
 </sst>
 </file>
@@ -617,7 +617,8 @@
   <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.453125" customWidth="1"/>
     <col min="4" max="4" width="41" customWidth="1"/>
   </cols>
   <sheetData>
@@ -728,10 +729,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" t="s">
         <v>84</v>
-      </c>
-      <c r="C7" t="s">
-        <v>73</v>
       </c>
       <c r="D7" t="s">
         <v>42</v>
@@ -745,7 +746,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
         <v>70</v>
@@ -762,10 +763,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
         <v>54</v>
@@ -779,10 +780,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
         <v>52</v>
@@ -796,10 +797,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
         <v>48</v>
@@ -813,10 +814,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
         <v>46</v>
@@ -830,7 +831,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
         <v>66</v>
@@ -847,10 +848,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
         <v>50</v>
@@ -864,7 +865,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
         <v>69</v>
@@ -881,7 +882,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
         <v>67</v>
@@ -898,10 +899,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
         <v>44</v>
@@ -915,7 +916,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
         <v>68</v>
@@ -932,10 +933,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
         <v>56</v>
@@ -949,7 +950,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
         <v>64</v>
@@ -966,10 +967,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
         <v>62</v>
@@ -983,7 +984,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
         <v>71</v>
@@ -1000,7 +1001,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
         <v>65</v>
@@ -1017,10 +1018,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
         <v>58</v>
@@ -1034,7 +1035,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
         <v>72</v>
@@ -1051,10 +1052,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
         <v>60</v>

--- a/faq.xlsx
+++ b/faq.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutomatedTelegram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1B7CB9-9E65-405F-930C-1C73022FBEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82352D1D-DA13-49D2-A8C9-A0CF6F1FDC56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="87">
   <si>
     <t>id</t>
   </si>
@@ -275,6 +275,12 @@
   </si>
   <si>
     <t>Account creation, (ការបង្កើតគណនី), បើកអាខោន</t>
+  </si>
+  <si>
+    <t>image_url</t>
+  </si>
+  <si>
+    <t>https://postimg.cc/47hpX32P</t>
   </si>
 </sst>
 </file>
@@ -310,8 +316,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -614,15 +623,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="12.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37.453125" customWidth="1"/>
     <col min="4" max="4" width="41" customWidth="1"/>
+    <col min="5" max="5" width="73.54296875" customWidth="1"/>
+    <col min="6" max="6" width="14.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -635,11 +646,14 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -652,11 +666,11 @@
       <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -669,11 +683,11 @@
       <c r="D3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -686,11 +700,11 @@
       <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -703,11 +717,11 @@
       <c r="D5" t="s">
         <v>23</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -720,11 +734,14 @@
       <c r="D6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -737,11 +754,11 @@
       <c r="D7" t="s">
         <v>42</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -754,11 +771,11 @@
       <c r="D8" t="s">
         <v>36</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -771,11 +788,11 @@
       <c r="D9" t="s">
         <v>54</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -788,11 +805,11 @@
       <c r="D10" t="s">
         <v>52</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -805,11 +822,11 @@
       <c r="D11" t="s">
         <v>48</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -822,11 +839,11 @@
       <c r="D12" t="s">
         <v>46</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -839,11 +856,11 @@
       <c r="D13" t="s">
         <v>28</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -856,11 +873,11 @@
       <c r="D14" t="s">
         <v>50</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -873,11 +890,11 @@
       <c r="D15" t="s">
         <v>34</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -890,7 +907,7 @@
       <c r="D16" t="s">
         <v>30</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>31</v>
       </c>
     </row>
@@ -907,7 +924,7 @@
       <c r="D17" t="s">
         <v>44</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="1" t="s">
         <v>45</v>
       </c>
     </row>
@@ -924,7 +941,7 @@
       <c r="D18" t="s">
         <v>32</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="1" t="s">
         <v>33</v>
       </c>
     </row>
@@ -941,7 +958,7 @@
       <c r="D19" t="s">
         <v>56</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="1" t="s">
         <v>57</v>
       </c>
     </row>
@@ -958,7 +975,7 @@
       <c r="D20" t="s">
         <v>24</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -975,7 +992,7 @@
       <c r="D21" t="s">
         <v>62</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="1" t="s">
         <v>63</v>
       </c>
     </row>
@@ -992,7 +1009,7 @@
       <c r="D22" t="s">
         <v>38</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="1" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1009,7 +1026,7 @@
       <c r="D23" t="s">
         <v>26</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="1" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1026,7 +1043,7 @@
       <c r="D24" t="s">
         <v>58</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="1" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1043,7 +1060,7 @@
       <c r="D25" t="s">
         <v>40</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="1" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1060,7 +1077,7 @@
       <c r="D26" t="s">
         <v>60</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="1" t="s">
         <v>61</v>
       </c>
     </row>

--- a/faq.xlsx
+++ b/faq.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutomatedTelegram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82352D1D-DA13-49D2-A8C9-A0CF6F1FDC56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A7B118-817A-472C-B16C-5038EA1B5B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,15 +40,9 @@
     <t>Our basic plan starts at $10/month.</t>
   </si>
   <si>
-    <t>We are located at 123 Main St.</t>
-  </si>
-  <si>
     <t>What are your business hours?</t>
   </si>
   <si>
-    <t>We are open 9 AM to 5 PM, Mon-Fri.</t>
-  </si>
-  <si>
     <t>You can click on the deposit tab-&gt;Scan QR to process it.</t>
   </si>
   <si>
@@ -280,7 +274,13 @@
     <t>image_url</t>
   </si>
   <si>
-    <t>https://postimg.cc/47hpX32P</t>
+    <t>https://postimg.cc/wybHxJZq</t>
+  </si>
+  <si>
+    <t>ខាងប្អូនមានទីតាំងនៅទីក្រុងភ្នំពេញ</t>
+  </si>
+  <si>
+    <t>យើងធ្វើការ 24h/24h</t>
   </si>
 </sst>
 </file>
@@ -650,7 +650,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -658,13 +658,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
         <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>5</v>
@@ -675,16 +675,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -692,16 +692,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -709,16 +709,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -726,359 +726,359 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D25" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
